--- a/tame_output/ON/bt/strategyON_20230829.xlsx
+++ b/tame_output/ON/bt/strategyON_20230829.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,7 +623,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.4%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -767,7 +767,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -809,7 +809,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-10.5%</t>
+          <t>-10.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -916,11 +916,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,12 +929,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.8%</t>
+          <t>101.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1069,11 +1069,11 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>97.6%</t>
+          <t>97.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>133.0%</t>
+          <t>132.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>4.05</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-27</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>127.5%</t>
+          <t>127.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8.7%</t>
+          <t>8.6%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1703"/>
+  <dimension ref="A1:G1704"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40679,7 +40679,7 @@
         <v>45165</v>
       </c>
       <c r="B1703" t="n">
-        <v>2.767539870835575</v>
+        <v>2.766977653385391</v>
       </c>
       <c r="C1703" t="n">
         <v>2.898366474365474</v>
@@ -40695,6 +40695,29 @@
       </c>
       <c r="G1703" t="n">
         <v>4.197208932544052</v>
+      </c>
+    </row>
+    <row r="1704">
+      <c r="A1704" s="2" t="n">
+        <v>45166</v>
+      </c>
+      <c r="B1704" t="n">
+        <v>2.769506775385254</v>
+      </c>
+      <c r="C1704" t="n">
+        <v>2.898149615933988</v>
+      </c>
+      <c r="D1704" t="n">
+        <v>1.545667290826573</v>
+      </c>
+      <c r="E1704" t="n">
+        <v>3.516060107950871</v>
+      </c>
+      <c r="F1704" t="n">
+        <v>2.164737430297627</v>
+      </c>
+      <c r="G1704" t="n">
+        <v>4.196992074112566</v>
       </c>
     </row>
   </sheetData>
